--- a/data/trans_orig/IP09B01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP09B01-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14402</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>12826</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21531</t>
+          <t>21512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25811</t>
+          <t>25471</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34949</t>
+          <t>34772</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,41%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14784</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>17241</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>17568</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9558</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16692</t>
+          <t>17376</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>19498</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24193</t>
+          <t>24109</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34547</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>20162</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29434</t>
+          <t>29982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41587</t>
+          <t>41303</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47642</t>
+          <t>48345</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60804</t>
+          <t>61351</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81647</t>
+          <t>81807</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99940</t>
+          <t>99351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>72,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25283</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>20139</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33848</t>
+          <t>33145</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36267</t>
+          <t>36856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54560</t>
+          <t>54400</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13636</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25445</t>
+          <t>25389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,03%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>46,18%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20362</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19987</t>
+          <t>20295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26658</t>
+          <t>26074</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38051</t>
+          <t>38088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,04%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>15081</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10767</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19445</t>
+          <t>19885</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>20472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>32486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>14504</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14144</t>
+          <t>14081</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21013</t>
+          <t>21232</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23505</t>
+          <t>23755</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>33136</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,4%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>11400</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21031</t>
+          <t>20781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,66%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18466</t>
+          <t>18268</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11214</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20012</t>
+          <t>20505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25812</t>
+          <t>25405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36925</t>
+          <t>36441</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>76,74%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>14259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10563</t>
+          <t>11047</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21676</t>
+          <t>22083</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46455</t>
+          <t>46450</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60424</t>
+          <t>59996</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51812</t>
+          <t>52596</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68059</t>
+          <t>68499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103352</t>
+          <t>103227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125068</t>
+          <t>124300</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21818</t>
+          <t>22246</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35787</t>
+          <t>35792</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30496</t>
+          <t>30056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46743</t>
+          <t>45959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55730</t>
+          <t>56498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77446</t>
+          <t>77571</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,9%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,9%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>13666</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17688</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>27777</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>12888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11951</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>22245</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6797</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>68,33%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7273</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,99%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11098</t>
+          <t>10746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>18464</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,36%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>53,23%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31947</t>
+          <t>31256</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>23760</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35626</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47336</t>
+          <t>47433</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62952</t>
+          <t>63783</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15867</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26633</t>
+          <t>26513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>16214</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28610</t>
+          <t>27687</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35618</t>
+          <t>34787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51234</t>
+          <t>51137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>15222</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23400</t>
+          <t>23382</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24199</t>
+          <t>24328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33915</t>
+          <t>33532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>549</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14941</t>
+          <t>15209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20738</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20364</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>28826</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40317</t>
+          <t>40252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,11%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13985</t>
+          <t>13636</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>18469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10246</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18227</t>
+          <t>18262</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20934</t>
+          <t>20394</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30069</t>
+          <t>29979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>15075</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>42,5%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12517</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20837</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20608</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31675</t>
+          <t>31577</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>71,97%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23269</t>
+          <t>23516</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,6%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41428</t>
+          <t>41701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53707</t>
+          <t>53764</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58373</t>
+          <t>58136</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79100</t>
+          <t>79103</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105685</t>
+          <t>105698</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128287</t>
+          <t>130081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22120</t>
+          <t>21847</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40656</t>
+          <t>40893</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>32497</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56893</t>
+          <t>56880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP09B01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP09B01-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6789</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13030</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>63,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>41,85%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>80,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6189</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3277</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8375</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3350</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8419</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>63,38%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>85,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10307</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7006</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13109</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>63,53%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12280</t>
+          <t>12172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,13%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5917</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3194</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9435</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>58,15%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3576</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1390</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>36,62%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>66,45%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5917</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9218</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>53,16%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16224</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16224</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16224</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9765</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>9765</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>9765</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>16224</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>16224</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>16224</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17538</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13362</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21536</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>63,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>48,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>77,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>13109</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9961</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14407</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10577</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14417</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>87,24%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>66,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>95,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>17538</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12826</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>21512</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>63,35%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25471</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34772</t>
+          <t>34682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,2%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10148</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6150</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14324</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>36,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>51,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1917</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5065</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4449</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>12,76%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>33,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>10148</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>6174</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>14860</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>36,65%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>27686</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>27686</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>27686</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>15026</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>15026</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>15026</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>27686</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>27686</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>27686</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10774</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7593</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13323</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>70,11%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>49,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>86,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3058</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5402</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5376</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>38,86%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>68,65%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10774</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7470</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13337</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>70,11%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17568</t>
+          <t>17231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>74,16%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4592</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7773</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>4811</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6663</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2493</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6757</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>61,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,35%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>84,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4592</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7896</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>29,89%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15366</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15366</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15366</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>7869</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>7869</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>7869</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>15366</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>15366</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15366</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16290</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12150</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18939</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>73,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>54,69%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>85,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>13394</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9558</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17376</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9402</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17083</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>60,73%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>43,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>78,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16290</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12315</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19498</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>73,33%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24109</t>
+          <t>24339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34474</t>
+          <t>34822</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5925</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3276</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10065</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>45,31%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4680</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12498</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4973</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12654</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>39,27%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>56,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>5925</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2717</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9900</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>26,67%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20162</t>
+          <t>19932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>22215</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22215</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22215</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>22056</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>22056</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>22056</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>22215</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>22215</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>22215</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54908</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>47648</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>61161</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>58,47%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>75,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>35751</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29982</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>41303</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>29720</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>40835</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>65,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>54,79%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>75,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>54908</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>48345</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>61351</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81807</t>
+          <t>81973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99351</t>
+          <t>100480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26582</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20329</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33842</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>18966</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13414</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24735</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>13882</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24997</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>26582</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>20139</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>33145</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>32,62%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36856</t>
+          <t>35727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54400</t>
+          <t>54234</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>81490</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>81490</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>81490</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>54717</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>54717</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>54717</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>81490</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>81490</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>81490</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10994</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7369</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13904</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>68,08%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45,63%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10533</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6993</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12692</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7258</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12726</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>74,89%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>49,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>90,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10994</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7486</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13896</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>68,08%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16263</t>
+          <t>16077</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25389</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5155</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2245</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8780</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54,37%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3532</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1373</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7072</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6807</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>25,11%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>50,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5155</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2253</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>8663</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,92%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13951</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16149</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16149</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16149</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>14065</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>14065</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>14065</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>16149</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>16149</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>16149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15703</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11084</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19971</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>51,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>36,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>64,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16719</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12725</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20468</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12821</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>20449</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>60,13%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>45,76%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>73,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>15703</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10869</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>20295</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>51,06%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26074</t>
+          <t>25435</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38088</t>
+          <t>37866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,66%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15051</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10783</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19670</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>48,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>35,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>63,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>11087</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7338</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15081</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7357</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>14985</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>39,87%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>26,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>54,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>15051</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>10459</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>19885</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>48,94%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20472</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32486</t>
+          <t>33125</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>56,57%</t>
         </is>
       </c>
     </row>
@@ -3244,52 +3244,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>30754</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>30754</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>30754</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>27806</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>27806</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>27806</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>30754</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>30754</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>30754</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17867</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13804</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21107</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>70,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>54,58%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>83,45%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10912</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7353</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14504</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7541</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14330</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>56,71%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>75,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17867</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14081</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>21232</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>70,64%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23755</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33136</t>
+          <t>33714</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>75,7%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7426</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4186</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11489</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8331</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4739</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11890</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4913</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>11702</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>43,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>24,63%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>61,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7426</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4061</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>11212</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>29,36%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20781</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,76%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25293</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>25293</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>25293</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>19243</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>19243</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>19243</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>25293</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>25293</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>25293</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16175</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11861</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20592</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>61,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>45,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>78,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>15384</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11609</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18268</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>11508</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18319</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>72,81%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>54,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>86,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16175</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20505</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>61,36%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25405</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36441</t>
+          <t>36342</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,53%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10185</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5768</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14499</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>55,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5744</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2860</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9519</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2809</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9620</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>27,19%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>45,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>10185</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>5855</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>14259</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>38,64%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22083</t>
+          <t>21903</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>26360</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>26360</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>26360</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>21128</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>21128</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>21128</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>26360</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>26360</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>26360</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>60738</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53340</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>69245</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>61,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>54,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,26%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>53548</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>46450</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>59996</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>45792</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>60211</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>65,11%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>56,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>72,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>60738</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>52596</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>68499</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>61,63%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103227</t>
+          <t>102905</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124300</t>
+          <t>124602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,92%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>37817</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>29310</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>45215</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29,74%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>28694</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>22246</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>35792</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>22031</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>36450</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,89%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>37817</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>30056</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>45959</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>38,37%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56498</t>
+          <t>56196</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77571</t>
+          <t>77893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>98555</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>98555</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>98555</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>82242</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>82242</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>82242</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>98555</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>98555</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>98555</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6340</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3487</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8429</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,3%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>35,92%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2616</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5314</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5547</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>32,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6340</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3546</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8437</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>65,3%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>12655</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3369</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6222</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,7%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,18%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>64,08%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>5553</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2855</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2622</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7462</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>67,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34,95%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>91,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3369</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1272</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6163</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>34,7%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12714</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9709</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9709</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9709</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>8169</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>8169</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>8169</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9709</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9709</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11853</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15208</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>59,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>39,83%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>75,88%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>10368</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6708</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13666</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7014</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14044</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>52,91%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>34,23%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>69,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11853</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7897</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15196</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>59,14%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27777</t>
+          <t>27463</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8188</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4833</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12058</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>40,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24,12%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>60,17%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>9228</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5930</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12888</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>5552</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>12582</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>47,09%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>30,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>65,77%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>8188</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>4845</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>12144</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>40,86%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11859</t>
+          <t>12173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22245</t>
+          <t>22495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,76%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>19596</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>19596</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>19596</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>20041</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>20041</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>20041</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4215</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1759</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6789</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>46,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>74,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4840</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2387</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7328</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2610</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7012</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>53,73%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>81,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4215</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1795</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6797</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>46,48%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>12324</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,18%</t>
         </is>
       </c>
     </row>
@@ -5421,67 +5421,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>4853</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>53,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>80,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>4168</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1680</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6621</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6398</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>46,27%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>73,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4853</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2271</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7273</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>53,52%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12290</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9068</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9068</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9068</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>9008</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>9008</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>9008</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9068</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9068</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,74 +5646,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6912</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4018</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9824</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>54,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>77,79%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8191</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4767</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>9704</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>79,14%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>46,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>50,91%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>93,76%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6912</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3655</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9754</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>28,94%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>77,24%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>21</t>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>81,1%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5717</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8611</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>45,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>22,21%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2159</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5583</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5081</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>20,86%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>6,24%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>53,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>5717</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2875</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>8974</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>45,27%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>22,76%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>12117</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12629</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12629</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>12629</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>10350</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>10350</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>10350</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>12629</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>12629</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>12629</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29320</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23419</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35223</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>56,99%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>45,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>26016</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>20610</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>31256</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>20224</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>31287</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>55,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>43,74%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>29320</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>23760</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>35233</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>56,99%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47433</t>
+          <t>46415</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63783</t>
+          <t>62759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>63,67%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22127</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16224</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>28028</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>43,01%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>54,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>21107</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>15867</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26513</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>15836</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>26899</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>44,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,67%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>56,26%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>22127</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>16214</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>27687</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>43,01%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34787</t>
+          <t>35811</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51137</t>
+          <t>52155</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>17653</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>20161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20423</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>29787</t>
+          <t>27433</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24328</t>
+          <t>23291</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33532</t>
+          <t>31118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7510</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,4%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2641</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5426</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>45,19%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3508</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>954</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20633</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20633</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20633</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12006</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12006</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12006</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14432</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10125</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18127</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>61,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>43,44%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>77,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18519</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15209</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20825</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>86,7%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>71,2%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>97,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16442</t>
+          <t>13234</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12299</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>15160</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>34961</t>
+          <t>27667</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28826</t>
+          <t>22480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40252</t>
+          <t>31789</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8875</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13182</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>38,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>56,56%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2841</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6151</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13636</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>12334</t>
+          <t>11787</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>16974</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>43,02%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>23307</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>23307</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>23307</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>21360</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>21360</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>21360</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>14762</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>10550</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>17750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15067</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25880</t>
+          <t>25752</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20394</t>
+          <t>20566</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29979</t>
+          <t>29422</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>85,0%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5096</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9308</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>25,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3696</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7317</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>25,47%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>50,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10590</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15075</t>
+          <t>14050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>40,59%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19858</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19858</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19858</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>14510</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>14510</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14510</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>34616</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>34616</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>34616</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15394</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11004</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19257</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>61,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>43,89%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9427</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5651</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12425</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>60,15%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,06%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>79,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16592</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>24528</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>19196</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31577</t>
+          <t>29428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,24%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9679</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5816</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14069</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>56,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>6246</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3248</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10022</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>39,85%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11612</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16899</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>17858</t>
+          <t>16211</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23516</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>25073</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>25073</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>25073</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>15673</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>15673</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>15673</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>62241</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53751</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>70273</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>70,03%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>60,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>48125</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>41701</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>53764</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65,62%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>84,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>68522</t>
+          <t>43139</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58136</t>
+          <t>37389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79103</t>
+          <t>48108</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>116648</t>
+          <t>105380</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105698</t>
+          <t>94707</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130081</t>
+          <t>115901</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>78,34%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26630</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18598</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>35120</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>29,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>15423</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>9784</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>21847</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30507</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40893</t>
+          <t>21693</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>45930</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>32052</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56880</t>
+          <t>53246</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
